--- a/data/outputs/Entity_Reconciliation.xlsx
+++ b/data/outputs/Entity_Reconciliation.xlsx
@@ -623,12 +623,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Endless (Matt Dalio) and E-line</t>
+          <t>E-Line Ventures</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Confirmed by user 2026-08-15: same folder houses both Endless and E-line deals.</t>
+          <t>RESOLVED 2026-08-16: split from the previously-merged 'Endless (Matt Dalio) and E-line' register entity into its own entity ('E-Line Ventures') - confirmed as a legally distinct company via signed SPA/Issuance Letter. See register confirmed_by for full citation.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -890,12 +890,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Endless (Matt Dalio) and E-line</t>
+          <t>Endless Studios</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Confirmed by user 2026-08-15</t>
+          <t>RESOLVED 2026-08-16: split from the previously-merged 'Endless (Matt Dalio) and E-line' register entity into its own entity ('Endless Studios') - confirmed as a legally distinct company via signed SPA/Issuance Letter. See register confirmed_by for full citation.</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MGX I Strategic Co-invest LP</t>
+          <t>MGX I Strategic Co-Invest LP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulk-confirmed (&gt;=0.6 confidence) by user 2026-08-15</t>
+          <t>RESOLVED 2026-08-16: fixed a case-sensitivity mismatch - this tracker name previously mapped to 'MGX I Strategic Co-invest LP' (lowercase i) while the actual cashflow/valuation extract uses 'MGX I Strategic Co-Invest LP' (capital I), causing this deal's cashflow join to silently return $0. Normalized to match.</t>
         </is>
       </c>
       <c r="D34" t="n">
